--- a/data2.xlsx
+++ b/data2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\THOMSON_J\Documents\offline files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD466DE8-F007-4942-A59D-3A29E2875E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB79F03D-0724-4E81-954F-34DD2E3BF4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5430" windowWidth="38640" windowHeight="21120" xr2:uid="{6A2D75CF-DED8-47D5-BE49-E34FC45C24DD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{6A2D75CF-DED8-47D5-BE49-E34FC45C24DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -827,7 +827,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C919F51F-D068-4207-A728-1B1A2EAAFF8C}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I851"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -869,7 +868,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -899,7 +898,7 @@
         <v>-2.8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -929,7 +928,7 @@
         <v>-2.89</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -959,7 +958,7 @@
         <v>21.35</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -989,7 +988,7 @@
         <v>-1.61</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1019,7 +1018,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1049,7 +1048,7 @@
         <v>-8.8800000000000008</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -1079,7 +1078,7 @@
         <v>-2.5500000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1109,7 +1108,7 @@
         <v>-4.9899999999999949</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1139,7 +1138,7 @@
         <v>-8.18</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1169,7 +1168,7 @@
         <v>-8.7199999999999704</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1199,7 +1198,7 @@
         <v>-11.379999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1229,7 +1228,7 @@
         <v>-8.82</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -1259,7 +1258,7 @@
         <v>4.8499999999999943</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -1289,7 +1288,7 @@
         <v>0.97999999999999865</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1319,7 +1318,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -1349,7 +1348,7 @@
         <v>18.09</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1379,7 +1378,7 @@
         <v>-35.49</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -1409,7 +1408,7 @@
         <v>-2.9499999999999744</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -1439,7 +1438,7 @@
         <v>1.3500000000000085</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -1469,7 +1468,7 @@
         <v>20.64</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -1499,7 +1498,7 @@
         <v>-2.93</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -1529,7 +1528,7 @@
         <v>-5.73</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -1559,7 +1558,7 @@
         <v>-1.78</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -1589,7 +1588,7 @@
         <v>-5.2</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -1619,7 +1618,7 @@
         <v>-29.709999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -1649,7 +1648,7 @@
         <v>-7.4899999999999993</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -1679,7 +1678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1709,7 +1708,7 @@
         <v>-16.82</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -1739,7 +1738,7 @@
         <v>-5.0999999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -1769,7 +1768,7 @@
         <v>-13.790000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -1799,7 +1798,7 @@
         <v>-11.61</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1829,7 +1828,7 @@
         <v>-1.24</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1859,7 +1858,7 @@
         <v>12.260000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1889,7 +1888,7 @@
         <v>-4.1000000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1919,7 +1918,7 @@
         <v>-8.34</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1949,7 +1948,7 @@
         <v>-34.74</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -1979,7 +1978,7 @@
         <v>-7.76</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -2009,7 +2008,7 @@
         <v>-31.709999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -2039,7 +2038,7 @@
         <v>-2.99</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -2069,7 +2068,7 @@
         <v>-2.59</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -2099,7 +2098,7 @@
         <v>-2.92</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -2129,7 +2128,7 @@
         <v>-32.3400000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -2159,7 +2158,7 @@
         <v>242.2</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -2189,7 +2188,7 @@
         <v>32.159999999999982</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -2219,7 +2218,7 @@
         <v>-2.74</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -2249,7 +2248,7 @@
         <v>-2.37</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -2279,7 +2278,7 @@
         <v>-8.5399999999999991</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -2309,7 +2308,7 @@
         <v>-8.19</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -2369,7 +2368,7 @@
         <v>-2.12</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -2399,7 +2398,7 @@
         <v>31.71</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -2429,7 +2428,7 @@
         <v>5.0300000000000011</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -2459,7 +2458,7 @@
         <v>-2.9</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -2489,7 +2488,7 @@
         <v>-5.8</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -2519,7 +2518,7 @@
         <v>-5.69</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -2549,7 +2548,7 @@
         <v>-2.74</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -2579,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -2609,7 +2608,7 @@
         <v>-20.07</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -2639,7 +2638,7 @@
         <v>-2.34</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -2669,7 +2668,7 @@
         <v>-0.39</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -2699,7 +2698,7 @@
         <v>-2.73</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -2729,7 +2728,7 @@
         <v>-12.57</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -2759,7 +2758,7 @@
         <v>-32.24</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -2789,7 +2788,7 @@
         <v>3.4299999999999997</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -2819,7 +2818,7 @@
         <v>-11.389999999999993</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -2849,7 +2848,7 @@
         <v>-4.58</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -2879,7 +2878,7 @@
         <v>-4.5</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -2909,7 +2908,7 @@
         <v>31.580000000000009</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -2939,7 +2938,7 @@
         <v>-4.9400000000000004</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>5</v>
       </c>
@@ -2969,7 +2968,7 @@
         <v>8.5300000000000011</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -2999,7 +2998,7 @@
         <v>-4.8699999999999992</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -3029,7 +3028,7 @@
         <v>-2.4700000000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -3059,7 +3058,7 @@
         <v>-3.55</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -3089,7 +3088,7 @@
         <v>-1.02</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -3119,7 +3118,7 @@
         <v>22.05</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -3149,7 +3148,7 @@
         <v>-1.93</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -3179,7 +3178,7 @@
         <v>-0.77</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -3209,7 +3208,7 @@
         <v>-11.61</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -3239,7 +3238,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -3269,7 +3268,7 @@
         <v>41.69</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>5</v>
       </c>
@@ -3299,7 +3298,7 @@
         <v>-1.1000000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -3329,7 +3328,7 @@
         <v>-57.389999999999993</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -3359,7 +3358,7 @@
         <v>39.68</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -3389,7 +3388,7 @@
         <v>-3.43</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>5</v>
       </c>
@@ -3419,7 +3418,7 @@
         <v>-1.6099999999999994</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -3449,7 +3448,7 @@
         <v>22.08</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -3479,7 +3478,7 @@
         <v>45.269999999999953</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -3509,7 +3508,7 @@
         <v>8.8700000000000045</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -3539,7 +3538,7 @@
         <v>120.01</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>5</v>
       </c>
@@ -3569,7 +3568,7 @@
         <v>-32.749999999999943</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>5</v>
       </c>
@@ -3599,7 +3598,7 @@
         <v>-13.060000000000009</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -3629,7 +3628,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -3659,7 +3658,7 @@
         <v>-1.9100000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>5</v>
       </c>
@@ -3689,7 +3688,7 @@
         <v>-2.92</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>5</v>
       </c>
@@ -3719,7 +3718,7 @@
         <v>14.28</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -3749,7 +3748,7 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -3779,7 +3778,7 @@
         <v>-1.58</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>5</v>
       </c>
@@ -3809,7 +3808,7 @@
         <v>17.350000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>5</v>
       </c>
@@ -3839,7 +3838,7 @@
         <v>-1.95</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>5</v>
       </c>
@@ -3869,7 +3868,7 @@
         <v>-19.649999999999999</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -3899,7 +3898,7 @@
         <v>-1.37</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>5</v>
       </c>
@@ -3929,7 +3928,7 @@
         <v>-6.4</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>5</v>
       </c>
@@ -3959,7 +3958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>5</v>
       </c>
@@ -3989,7 +3988,7 @@
         <v>24.74</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>5</v>
       </c>
@@ -4019,7 +4018,7 @@
         <v>-2.61</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>5</v>
       </c>
@@ -4049,7 +4048,7 @@
         <v>-13.81</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>5</v>
       </c>
@@ -4079,7 +4078,7 @@
         <v>-3.2099999999999995</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>5</v>
       </c>
@@ -4109,7 +4108,7 @@
         <v>-19.880000000000003</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -4139,7 +4138,7 @@
         <v>-2.89</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -4169,7 +4168,7 @@
         <v>-5.5299999999999994</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>5</v>
       </c>
@@ -4199,7 +4198,7 @@
         <v>-1.45</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -4229,7 +4228,7 @@
         <v>-3.92</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>5</v>
       </c>
@@ -4259,7 +4258,7 @@
         <v>-1.85</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>5</v>
       </c>
@@ -4289,7 +4288,7 @@
         <v>-5.7600000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>5</v>
       </c>
@@ -4319,7 +4318,7 @@
         <v>-0.98</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>5</v>
       </c>
@@ -4349,7 +4348,7 @@
         <v>-65.920000000000044</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -4379,7 +4378,7 @@
         <v>78.86999999999999</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -4409,7 +4408,7 @@
         <v>-21.029999999999998</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -4439,7 +4438,7 @@
         <v>-4.41</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -4469,7 +4468,7 @@
         <v>-2.29</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -4499,7 +4498,7 @@
         <v>-4.18</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -4529,7 +4528,7 @@
         <v>-5.3800000000000008</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -4559,7 +4558,7 @@
         <v>-8.06</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -4589,7 +4588,7 @@
         <v>30.65</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -4619,7 +4618,7 @@
         <v>26.89</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>5</v>
       </c>
@@ -4649,7 +4648,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>5</v>
       </c>
@@ -4679,7 +4678,7 @@
         <v>14.930000000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -4709,7 +4708,7 @@
         <v>-2.4700000000000002</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>5</v>
       </c>
@@ -4739,7 +4738,7 @@
         <v>-2.6</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>5</v>
       </c>
@@ -4769,7 +4768,7 @@
         <v>-5.07</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -4799,7 +4798,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -4829,7 +4828,7 @@
         <v>-4.9200000000000017</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>5</v>
       </c>
@@ -4859,7 +4858,7 @@
         <v>-12.540000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>5</v>
       </c>
@@ -4889,7 +4888,7 @@
         <v>-2.6</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -4919,7 +4918,7 @@
         <v>-2.4700000000000002</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -4949,7 +4948,7 @@
         <v>-2.4700000000000002</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -4979,7 +4978,7 @@
         <v>3.8000000000000007</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -5009,7 +5008,7 @@
         <v>-1.63</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>5</v>
       </c>
@@ -5039,7 +5038,7 @@
         <v>-7.84</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>5</v>
       </c>
@@ -5069,7 +5068,7 @@
         <v>-0.95</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>5</v>
       </c>
@@ -5099,7 +5098,7 @@
         <v>-2.34</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>5</v>
       </c>
@@ -5129,7 +5128,7 @@
         <v>-2.15</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>5</v>
       </c>
@@ -5159,7 +5158,7 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>5</v>
       </c>
@@ -5189,7 +5188,7 @@
         <v>-3.1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>5</v>
       </c>
@@ -5219,7 +5218,7 @@
         <v>-9.92</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -5249,7 +5248,7 @@
         <v>-5.7</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>5</v>
       </c>
@@ -5279,7 +5278,7 @@
         <v>-2.92</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>5</v>
       </c>
@@ -5309,7 +5308,7 @@
         <v>-8.26</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>5</v>
       </c>
@@ -5339,7 +5338,7 @@
         <v>30.65</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>5</v>
       </c>
@@ -5369,7 +5368,7 @@
         <v>32.26</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -5399,7 +5398,7 @@
         <v>-1.76</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -5429,7 +5428,7 @@
         <v>-1.34</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -5459,7 +5458,7 @@
         <v>14.420000000000002</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>5</v>
       </c>
@@ -5489,7 +5488,7 @@
         <v>72.27</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -5519,7 +5518,7 @@
         <v>-15.770000000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>5</v>
       </c>
@@ -5549,7 +5548,7 @@
         <v>54.509999999999991</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>5</v>
       </c>
@@ -5579,7 +5578,7 @@
         <v>-41.629999999999995</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>5</v>
       </c>
@@ -5609,7 +5608,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>5</v>
       </c>
@@ -5639,7 +5638,7 @@
         <v>-28.979999999999997</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>5</v>
       </c>
@@ -5669,7 +5668,7 @@
         <v>-4.4500000000000028</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>5</v>
       </c>
@@ -5699,7 +5698,7 @@
         <v>19.11</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>5</v>
       </c>
@@ -5729,7 +5728,7 @@
         <v>-94.369999999998527</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>5</v>
       </c>
@@ -5759,7 +5758,7 @@
         <v>-53.679999999999993</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>5</v>
       </c>
@@ -5789,7 +5788,7 @@
         <v>-3.28</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>5</v>
       </c>
@@ -5819,7 +5818,7 @@
         <v>-5.1700000000000017</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>5</v>
       </c>
@@ -5849,7 +5848,7 @@
         <v>92.22999999999999</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>5</v>
       </c>
@@ -5879,7 +5878,7 @@
         <v>-5.01</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>5</v>
       </c>
@@ -5909,7 +5908,7 @@
         <v>2.7299999999999969</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -5939,7 +5938,7 @@
         <v>-36.08</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>5</v>
       </c>
@@ -5969,7 +5968,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>5</v>
       </c>
@@ -5999,7 +5998,7 @@
         <v>-14.060000000000002</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>5</v>
       </c>
@@ -6029,7 +6028,7 @@
         <v>-2.5299999999999998</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>5</v>
       </c>
@@ -6059,7 +6058,7 @@
         <v>-5.51</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -6089,7 +6088,7 @@
         <v>-1.29</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>5</v>
       </c>
@@ -6119,7 +6118,7 @@
         <v>19.569999999999997</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>5</v>
       </c>
@@ -6149,7 +6148,7 @@
         <v>-9.8800000000000008</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>5</v>
       </c>
@@ -6179,7 +6178,7 @@
         <v>-1.51</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>5</v>
       </c>
@@ -6209,7 +6208,7 @@
         <v>-0.54</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>5</v>
       </c>
@@ -6239,7 +6238,7 @@
         <v>-10.270000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>5</v>
       </c>
@@ -6269,7 +6268,7 @@
         <v>-21.909999999999989</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>5</v>
       </c>
@@ -6299,7 +6298,7 @@
         <v>0.68000000000000327</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>5</v>
       </c>
@@ -6329,7 +6328,7 @@
         <v>32.390000000000015</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>5</v>
       </c>
@@ -6359,7 +6358,7 @@
         <v>-15.27</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>5</v>
       </c>
@@ -6389,7 +6388,7 @@
         <v>-8.0299999999999994</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>5</v>
       </c>
@@ -6419,7 +6418,7 @@
         <v>-20.59</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>5</v>
       </c>
@@ -6449,7 +6448,7 @@
         <v>-13.640000000000002</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>5</v>
       </c>
@@ -6479,7 +6478,7 @@
         <v>-2.74</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>5</v>
       </c>
@@ -6509,7 +6508,7 @@
         <v>-66.930000000000007</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>5</v>
       </c>
@@ -6539,7 +6538,7 @@
         <v>-40.310000000000016</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>5</v>
       </c>
@@ -6569,7 +6568,7 @@
         <v>-6.52</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>5</v>
       </c>
@@ -6599,7 +6598,7 @@
         <v>11.540000000000006</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>5</v>
       </c>
@@ -6629,7 +6628,7 @@
         <v>-5.5399999999999991</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>5</v>
       </c>
@@ -6659,7 +6658,7 @@
         <v>-30.909999999999968</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>5</v>
       </c>
@@ -6689,7 +6688,7 @@
         <v>-28.13</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>5</v>
       </c>
@@ -6719,7 +6718,7 @@
         <v>-81.710000000000008</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>5</v>
       </c>
@@ -6749,7 +6748,7 @@
         <v>38.050000000000011</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>5</v>
       </c>
@@ -6779,7 +6778,7 @@
         <v>-0.41</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>5</v>
       </c>
@@ -6809,7 +6808,7 @@
         <v>-15.520000000000003</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>5</v>
       </c>
@@ -6839,7 +6838,7 @@
         <v>37.759999999999991</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>5</v>
       </c>
@@ -6869,7 +6868,7 @@
         <v>-34.989999999999981</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>5</v>
       </c>
@@ -6899,7 +6898,7 @@
         <v>-10.450000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>5</v>
       </c>
@@ -6929,7 +6928,7 @@
         <v>-32.220000000000006</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -6959,7 +6958,7 @@
         <v>-28.44</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>5</v>
       </c>
@@ -6989,7 +6988,7 @@
         <v>-5.42</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>5</v>
       </c>
@@ -7019,7 +7018,7 @@
         <v>9.6499999999999986</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>5</v>
       </c>
@@ -7049,7 +7048,7 @@
         <v>-57.699999999999903</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>5</v>
       </c>
@@ -7079,7 +7078,7 @@
         <v>-20.580000000000027</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>5</v>
       </c>
@@ -7109,7 +7108,7 @@
         <v>-2.36</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>5</v>
       </c>
@@ -7139,7 +7138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>5</v>
       </c>
@@ -7169,7 +7168,7 @@
         <v>-4.96</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>5</v>
       </c>
@@ -7199,7 +7198,7 @@
         <v>-13.449999999999998</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>5</v>
       </c>
@@ -7229,7 +7228,7 @@
         <v>2.7700000000000031</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>5</v>
       </c>
@@ -7259,7 +7258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>5</v>
       </c>
@@ -7289,7 +7288,7 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>5</v>
       </c>
@@ -7319,7 +7318,7 @@
         <v>-1.33</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>5</v>
       </c>
@@ -7349,7 +7348,7 @@
         <v>36.580000000000005</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>5</v>
       </c>
@@ -7379,7 +7378,7 @@
         <v>18.470000000000002</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>5</v>
       </c>
@@ -7409,7 +7408,7 @@
         <v>-2.4299999999999997</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>5</v>
       </c>
@@ -7439,7 +7438,7 @@
         <v>-66.419999999999987</v>
       </c>
     </row>
-    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>5</v>
       </c>
@@ -7469,7 +7468,7 @@
         <v>46.269999999999996</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>5</v>
       </c>
@@ -7499,7 +7498,7 @@
         <v>-1.23</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>5</v>
       </c>
@@ -7529,7 +7528,7 @@
         <v>-3.5499999999999989</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>5</v>
       </c>
@@ -7559,7 +7558,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>5</v>
       </c>
@@ -7589,7 +7588,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>5</v>
       </c>
@@ -7619,7 +7618,7 @@
         <v>-2.61</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>5</v>
       </c>
@@ -7649,7 +7648,7 @@
         <v>-5.24</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>5</v>
       </c>
@@ -7679,7 +7678,7 @@
         <v>-2.74</v>
       </c>
     </row>
-    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>5</v>
       </c>
@@ -7709,7 +7708,7 @@
         <v>32.28</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>5</v>
       </c>
@@ -7739,7 +7738,7 @@
         <v>-21.79</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>5</v>
       </c>
@@ -7769,7 +7768,7 @@
         <v>29.259999999999991</v>
       </c>
     </row>
-    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>5</v>
       </c>
@@ -7799,7 +7798,7 @@
         <v>12.549999999999997</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>5</v>
       </c>
@@ -7829,7 +7828,7 @@
         <v>-17.72</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>5</v>
       </c>
@@ -7859,7 +7858,7 @@
         <v>-0.9</v>
       </c>
     </row>
-    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>5</v>
       </c>
@@ -7889,7 +7888,7 @@
         <v>-20.78</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>5</v>
       </c>
@@ -7919,7 +7918,7 @@
         <v>-1.64</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>5</v>
       </c>
@@ -7949,7 +7948,7 @@
         <v>-13.18</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>5</v>
       </c>
@@ -7979,7 +7978,7 @@
         <v>61.679999999999993</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>5</v>
       </c>
@@ -8009,7 +8008,7 @@
         <v>20.939999999999998</v>
       </c>
     </row>
-    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>5</v>
       </c>
@@ -8039,7 +8038,7 @@
         <v>-0.86</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>5</v>
       </c>
@@ -8069,7 +8068,7 @@
         <v>-24.470000000000013</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>5</v>
       </c>
@@ -8099,7 +8098,7 @@
         <v>-0.83</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>5</v>
       </c>
@@ -8129,7 +8128,7 @@
         <v>-0.38000000000000611</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>5</v>
       </c>
@@ -8159,7 +8158,7 @@
         <v>-1.32</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>5</v>
       </c>
@@ -8189,7 +8188,7 @@
         <v>-0.72</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>5</v>
       </c>
@@ -8219,7 +8218,7 @@
         <v>-1.44</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>5</v>
       </c>
@@ -8249,7 +8248,7 @@
         <v>-6.75</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>5</v>
       </c>
@@ -8279,7 +8278,7 @@
         <v>7.0999999999999979</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>5</v>
       </c>
@@ -8309,7 +8308,7 @@
         <v>-0.89</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>5</v>
       </c>
@@ -8339,7 +8338,7 @@
         <v>-3.1799999999999997</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>5</v>
       </c>
@@ -8369,7 +8368,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>7</v>
       </c>
@@ -8399,7 +8398,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>7</v>
       </c>
@@ -8429,7 +8428,7 @@
         <v>-24.199999999999989</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>7</v>
       </c>
@@ -8459,7 +8458,7 @@
         <v>-0.24000000000000032</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>7</v>
       </c>
@@ -8489,7 +8488,7 @@
         <v>45.81</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>7</v>
       </c>
@@ -8519,7 +8518,7 @@
         <v>-2.74</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>7</v>
       </c>
@@ -8549,7 +8548,7 @@
         <v>-13.559999999999992</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>7</v>
       </c>
@@ -8579,7 +8578,7 @@
         <v>36.760000000000005</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>7</v>
       </c>
@@ -8609,7 +8608,7 @@
         <v>13.050000000000004</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>7</v>
       </c>
@@ -8639,7 +8638,7 @@
         <v>-4.32</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>7</v>
       </c>
@@ -8669,7 +8668,7 @@
         <v>19.23</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>7</v>
       </c>
@@ -8699,7 +8698,7 @@
         <v>-14.439999999999998</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>7</v>
       </c>
@@ -8729,7 +8728,7 @@
         <v>4.8099999999999952</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>7</v>
       </c>
@@ -8759,7 +8758,7 @@
         <v>-13.140000000000008</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>7</v>
       </c>
@@ -8789,7 +8788,7 @@
         <v>-100.54000000000005</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>7</v>
       </c>
@@ -8819,7 +8818,7 @@
         <v>-11.870000000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>7</v>
       </c>
@@ -8849,7 +8848,7 @@
         <v>58.829999999999991</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>7</v>
       </c>
@@ -8879,7 +8878,7 @@
         <v>-1.94</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>7</v>
       </c>
@@ -8909,7 +8908,7 @@
         <v>-42.9</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>7</v>
       </c>
@@ -8939,7 +8938,7 @@
         <v>17.929999999999978</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>7</v>
       </c>
@@ -8969,7 +8968,7 @@
         <v>-2.5300000000000002</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>7</v>
       </c>
@@ -8999,7 +8998,7 @@
         <v>-49.920000000000016</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>7</v>
       </c>
@@ -9029,7 +9028,7 @@
         <v>-137.17999999999972</v>
       </c>
     </row>
-    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>7</v>
       </c>
@@ -9059,7 +9058,7 @@
         <v>-73.980000000000018</v>
       </c>
     </row>
-    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>7</v>
       </c>
@@ -9089,7 +9088,7 @@
         <v>19.64</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>7</v>
       </c>
@@ -9119,7 +9118,7 @@
         <v>-4.3199999999999932</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>7</v>
       </c>
@@ -9149,7 +9148,7 @@
         <v>-42.560000000000173</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>7</v>
       </c>
@@ -9179,7 +9178,7 @@
         <v>-21.459999999999997</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>7</v>
       </c>
@@ -9209,7 +9208,7 @@
         <v>11.259999999999998</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>7</v>
       </c>
@@ -9239,7 +9238,7 @@
         <v>608.35999999999899</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>7</v>
       </c>
@@ -9269,7 +9268,7 @@
         <v>361.43999999999596</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>7</v>
       </c>
@@ -9299,7 +9298,7 @@
         <v>-1.92</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>7</v>
       </c>
@@ -9329,7 +9328,7 @@
         <v>-11.709999999999999</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>7</v>
       </c>
@@ -9359,7 +9358,7 @@
         <v>-2.14</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>7</v>
       </c>
@@ -9389,7 +9388,7 @@
         <v>47.83</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>7</v>
       </c>
@@ -9419,7 +9418,7 @@
         <v>17.299999999999997</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>7</v>
       </c>
@@ -9449,7 +9448,7 @@
         <v>-23.419999999999924</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>7</v>
       </c>
@@ -9479,7 +9478,7 @@
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>7</v>
       </c>
@@ -9509,7 +9508,7 @@
         <v>13.670000000000002</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>7</v>
       </c>
@@ -9539,7 +9538,7 @@
         <v>74.360000000000014</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>7</v>
       </c>
@@ -9569,7 +9568,7 @@
         <v>-552.46000000000015</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>7</v>
       </c>
@@ -9599,7 +9598,7 @@
         <v>30.220000000000006</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>52</v>
       </c>
@@ -9629,7 +9628,7 @@
         <v>-0.36</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>52</v>
       </c>
@@ -9659,7 +9658,7 @@
         <v>-33.21</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>52</v>
       </c>
@@ -9689,7 +9688,7 @@
         <v>1050.33</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>52</v>
       </c>
@@ -9719,7 +9718,7 @@
         <v>-3.91</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>52</v>
       </c>
@@ -9749,7 +9748,7 @@
         <v>-808.86000000000172</v>
       </c>
     </row>
-    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>52</v>
       </c>
@@ -9779,7 +9778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>52</v>
       </c>
@@ -9809,7 +9808,7 @@
         <v>-1.53</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>52</v>
       </c>
@@ -9839,7 +9838,7 @@
         <v>-11.73</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>52</v>
       </c>
@@ -9869,7 +9868,7 @@
         <v>-15.209999999999999</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>52</v>
       </c>
@@ -9899,7 +9898,7 @@
         <v>172.62</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>52</v>
       </c>
@@ -10139,7 +10138,7 @@
         <v>18.219999999999985</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>52</v>
       </c>
@@ -10169,7 +10168,7 @@
         <v>850.54</v>
       </c>
     </row>
-    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>52</v>
       </c>
@@ -10199,7 +10198,7 @@
         <v>228.28000000000003</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>52</v>
       </c>
@@ -10229,7 +10228,7 @@
         <v>-52.69</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>52</v>
       </c>
@@ -10259,7 +10258,7 @@
         <v>-53.930000000000014</v>
       </c>
     </row>
-    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>52</v>
       </c>
@@ -10289,7 +10288,7 @@
         <v>-1112.8100000000002</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>52</v>
       </c>
@@ -10319,7 +10318,7 @@
         <v>-910.94000000000028</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>52</v>
       </c>
@@ -10349,7 +10348,7 @@
         <v>-12.149999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>52</v>
       </c>
@@ -10379,7 +10378,7 @@
         <v>-21.92</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>52</v>
       </c>
@@ -10409,7 +10408,7 @@
         <v>-16.069999999999993</v>
       </c>
     </row>
-    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>52</v>
       </c>
@@ -10469,7 +10468,7 @@
         <v>-114.39000000000004</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>52</v>
       </c>
@@ -10499,7 +10498,7 @@
         <v>-75.290000000000049</v>
       </c>
     </row>
-    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>52</v>
       </c>
@@ -10529,7 +10528,7 @@
         <v>-214.91000000000003</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>52</v>
       </c>
@@ -10559,7 +10558,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>52</v>
       </c>
@@ -10589,7 +10588,7 @@
         <v>62.47</v>
       </c>
     </row>
-    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>52</v>
       </c>
@@ -10619,7 +10618,7 @@
         <v>-329.47</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>52</v>
       </c>
@@ -10649,7 +10648,7 @@
         <v>-101.24999999999999</v>
       </c>
     </row>
-    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>52</v>
       </c>
@@ -10679,7 +10678,7 @@
         <v>-4.5200000000000005</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>52</v>
       </c>
@@ -10709,7 +10708,7 @@
         <v>7.6299999999999955</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>52</v>
       </c>
@@ -10739,7 +10738,7 @@
         <v>10.09</v>
       </c>
     </row>
-    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>52</v>
       </c>
@@ -10769,7 +10768,7 @@
         <v>122.58999999999999</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>52</v>
       </c>
@@ -10799,7 +10798,7 @@
         <v>-5.9099999999999993</v>
       </c>
     </row>
-    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>52</v>
       </c>
@@ -10829,7 +10828,7 @@
         <v>-102.88000000000001</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>52</v>
       </c>
@@ -10859,7 +10858,7 @@
         <v>-0.95000000000000018</v>
       </c>
     </row>
-    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>52</v>
       </c>
@@ -10889,7 +10888,7 @@
         <v>-235.63999999999984</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>52</v>
       </c>
@@ -10919,7 +10918,7 @@
         <v>-0.28000000000000003</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>52</v>
       </c>
@@ -10949,7 +10948,7 @@
         <v>9.2099999999999991</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>52</v>
       </c>
@@ -10979,7 +10978,7 @@
         <v>-0.38</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>52</v>
       </c>
@@ -11009,7 +11008,7 @@
         <v>805.0799999999997</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>52</v>
       </c>
@@ -11039,7 +11038,7 @@
         <v>33.08</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>52</v>
       </c>
@@ -11069,7 +11068,7 @@
         <v>-35.789999999999992</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>52</v>
       </c>
@@ -11099,7 +11098,7 @@
         <v>-16.78</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>52</v>
       </c>
@@ -11129,7 +11128,7 @@
         <v>-617.11</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>52</v>
       </c>
@@ -11159,7 +11158,7 @@
         <v>-22.599999999999998</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>52</v>
       </c>
@@ -11189,7 +11188,7 @@
         <v>-75.459999999999994</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>52</v>
       </c>
@@ -11219,7 +11218,7 @@
         <v>-4.79</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>52</v>
       </c>
@@ -11249,7 +11248,7 @@
         <v>-45.13</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>52</v>
       </c>
@@ -11279,7 +11278,7 @@
         <v>-48.350000000000016</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>52</v>
       </c>
@@ -11309,7 +11308,7 @@
         <v>27.86</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>52</v>
       </c>
@@ -11339,7 +11338,7 @@
         <v>49.449999999999996</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>52</v>
       </c>
@@ -11369,7 +11368,7 @@
         <v>-15.63</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>52</v>
       </c>
@@ -11399,7 +11398,7 @@
         <v>-63.75</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>52</v>
       </c>
@@ -11429,7 +11428,7 @@
         <v>-63.209999999999951</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>52</v>
       </c>
@@ -11459,7 +11458,7 @@
         <v>-111.19000000000001</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>52</v>
       </c>
@@ -11489,7 +11488,7 @@
         <v>-7.31</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>52</v>
       </c>
@@ -11519,7 +11518,7 @@
         <v>-101.13000000000001</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>52</v>
       </c>
@@ -11549,7 +11548,7 @@
         <v>80.920000000000016</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>52</v>
       </c>
@@ -11579,7 +11578,7 @@
         <v>-1.32</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>52</v>
       </c>
@@ -11609,7 +11608,7 @@
         <v>-4.09</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>52</v>
       </c>
@@ -11639,7 +11638,7 @@
         <v>666.59000000000026</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>52</v>
       </c>
@@ -11669,7 +11668,7 @@
         <v>-173.22000000000003</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>52</v>
       </c>
@@ -11699,7 +11698,7 @@
         <v>-51.74</v>
       </c>
     </row>
-    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>52</v>
       </c>
@@ -11729,7 +11728,7 @@
         <v>19.210000000000015</v>
       </c>
     </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>52</v>
       </c>
@@ -11759,7 +11758,7 @@
         <v>-770.94999999999959</v>
       </c>
     </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>52</v>
       </c>
@@ -11789,7 +11788,7 @@
         <v>-28.570000000000004</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>52</v>
       </c>
@@ -11819,7 +11818,7 @@
         <v>61.139999999999993</v>
       </c>
     </row>
-    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>52</v>
       </c>
@@ -11849,7 +11848,7 @@
         <v>19.129999999999995</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>52</v>
       </c>
@@ -11879,7 +11878,7 @@
         <v>429.82000000000005</v>
       </c>
     </row>
-    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>52</v>
       </c>
@@ -11909,7 +11908,7 @@
         <v>895.61999999999989</v>
       </c>
     </row>
-    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>52</v>
       </c>
@@ -12029,7 +12028,7 @@
         <v>-952.92000000000087</v>
       </c>
     </row>
-    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>52</v>
       </c>
@@ -12059,7 +12058,7 @@
         <v>-950.02000000000112</v>
       </c>
     </row>
-    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>52</v>
       </c>
@@ -12089,7 +12088,7 @@
         <v>1038.3400000000001</v>
       </c>
     </row>
-    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>52</v>
       </c>
@@ -12119,7 +12118,7 @@
         <v>565.20999999999992</v>
       </c>
     </row>
-    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>52</v>
       </c>
@@ -12149,7 +12148,7 @@
         <v>3.9099999999999984</v>
       </c>
     </row>
-    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>52</v>
       </c>
@@ -12179,7 +12178,7 @@
         <v>-11.58</v>
       </c>
     </row>
-    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>52</v>
       </c>
@@ -12209,7 +12208,7 @@
         <v>-1357.3300000000002</v>
       </c>
     </row>
-    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>52</v>
       </c>
@@ -12239,7 +12238,7 @@
         <v>-581.51000000000022</v>
       </c>
     </row>
-    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>52</v>
       </c>
@@ -12269,7 +12268,7 @@
         <v>-8.9699999999999989</v>
       </c>
     </row>
-    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>52</v>
       </c>
@@ -12299,7 +12298,7 @@
         <v>-113.48000000000002</v>
       </c>
     </row>
-    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>52</v>
       </c>
@@ -12329,7 +12328,7 @@
         <v>113.05999999999996</v>
       </c>
     </row>
-    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>52</v>
       </c>
@@ -12359,7 +12358,7 @@
         <v>-31.38000000000001</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>52</v>
       </c>
@@ -12389,7 +12388,7 @@
         <v>-71.449999999999989</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>52</v>
       </c>
@@ -12419,7 +12418,7 @@
         <v>-72.23</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>52</v>
       </c>
@@ -12449,7 +12448,7 @@
         <v>-245.99000000000007</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>52</v>
       </c>
@@ -12479,7 +12478,7 @@
         <v>-130.02000000000004</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>52</v>
       </c>
@@ -12509,7 +12508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>52</v>
       </c>
@@ -12539,7 +12538,7 @@
         <v>-12.709999999999999</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>52</v>
       </c>
@@ -12629,7 +12628,7 @@
         <v>12.840000000000003</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>52</v>
       </c>
@@ -12659,7 +12658,7 @@
         <v>86.21</v>
       </c>
     </row>
-    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>52</v>
       </c>
@@ -12689,7 +12688,7 @@
         <v>51.88000000000001</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>52</v>
       </c>
@@ -12719,7 +12718,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>52</v>
       </c>
@@ -12749,7 +12748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>52</v>
       </c>
@@ -12779,7 +12778,7 @@
         <v>-128.15999999999997</v>
       </c>
     </row>
-    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>52</v>
       </c>
@@ -12809,7 +12808,7 @@
         <v>-58.609999999999985</v>
       </c>
     </row>
-    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>52</v>
       </c>
@@ -12839,7 +12838,7 @@
         <v>-19.43</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>52</v>
       </c>
@@ -12869,7 +12868,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>52</v>
       </c>
@@ -12959,7 +12958,7 @@
         <v>-12.14</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>52</v>
       </c>
@@ -12989,7 +12988,7 @@
         <v>-15.52</v>
       </c>
     </row>
-    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>52</v>
       </c>
@@ -13019,7 +13018,7 @@
         <v>-1.6400000000000001</v>
       </c>
     </row>
-    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>52</v>
       </c>
@@ -13049,7 +13048,7 @@
         <v>595.15000000000009</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>52</v>
       </c>
@@ -13199,7 +13198,7 @@
         <v>-282.13999999999993</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>52</v>
       </c>
@@ -13229,7 +13228,7 @@
         <v>-2.25</v>
       </c>
     </row>
-    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>52</v>
       </c>
@@ -13259,7 +13258,7 @@
         <v>481.22000000000008</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>52</v>
       </c>
@@ -13289,7 +13288,7 @@
         <v>198.29999999999998</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>52</v>
       </c>
@@ -13319,7 +13318,7 @@
         <v>34.349999999999994</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>52</v>
       </c>
@@ -13349,7 +13348,7 @@
         <v>-7.5299999999999994</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>52</v>
       </c>
@@ -13379,7 +13378,7 @@
         <v>-595.19000000000005</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>52</v>
       </c>
@@ -13409,7 +13408,7 @@
         <v>-443.39000000000033</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>52</v>
       </c>
@@ -13439,7 +13438,7 @@
         <v>184.29000000000002</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>52</v>
       </c>
@@ -13469,7 +13468,7 @@
         <v>3.6199999999999974</v>
       </c>
     </row>
-    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>52</v>
       </c>
@@ -13499,7 +13498,7 @@
         <v>-48.100000000000016</v>
       </c>
     </row>
-    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>52</v>
       </c>
@@ -13529,7 +13528,7 @@
         <v>459.25999999999988</v>
       </c>
     </row>
-    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>52</v>
       </c>
@@ -13559,7 +13558,7 @@
         <v>-303.12999999999988</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>52</v>
       </c>
@@ -13589,7 +13588,7 @@
         <v>-21.720000000000006</v>
       </c>
     </row>
-    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>52</v>
       </c>
@@ -13619,7 +13618,7 @@
         <v>1014.89</v>
       </c>
     </row>
-    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>9</v>
       </c>
@@ -13649,7 +13648,7 @@
         <v>-67.61</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>9</v>
       </c>
@@ -13679,7 +13678,7 @@
         <v>-308.25000000000011</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>9</v>
       </c>
@@ -13709,7 +13708,7 @@
         <v>-2.0499999999999998</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>9</v>
       </c>
@@ -13739,7 +13738,7 @@
         <v>24.17</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>9</v>
       </c>
@@ -13769,7 +13768,7 @@
         <v>-474.07000000000079</v>
       </c>
     </row>
-    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>9</v>
       </c>
@@ -13799,7 +13798,7 @@
         <v>19.52</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>9</v>
       </c>
@@ -13829,7 +13828,7 @@
         <v>-8.34</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>9</v>
       </c>
@@ -13859,7 +13858,7 @@
         <v>-2.1500000000000004</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>9</v>
       </c>
@@ -13889,7 +13888,7 @@
         <v>-6.2299999999999986</v>
       </c>
     </row>
-    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>9</v>
       </c>
@@ -13919,7 +13918,7 @@
         <v>-132.09</v>
       </c>
     </row>
-    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>9</v>
       </c>
@@ -13949,7 +13948,7 @@
         <v>-2.66</v>
       </c>
     </row>
-    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>9</v>
       </c>
@@ -13979,7 +13978,7 @@
         <v>-3.52</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>9</v>
       </c>
@@ -14009,7 +14008,7 @@
         <v>-6.9499999999999993</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>9</v>
       </c>
@@ -14039,7 +14038,7 @@
         <v>-4.0699999999999994</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>9</v>
       </c>
@@ -14069,7 +14068,7 @@
         <v>134.88</v>
       </c>
     </row>
-    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>9</v>
       </c>
@@ -14099,7 +14098,7 @@
         <v>-40.72999999999999</v>
       </c>
     </row>
-    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>9</v>
       </c>
@@ -14129,7 +14128,7 @@
         <v>-0.16</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>9</v>
       </c>
@@ -14159,7 +14158,7 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>9</v>
       </c>
@@ -14189,7 +14188,7 @@
         <v>33.58</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>9</v>
       </c>
@@ -14219,7 +14218,7 @@
         <v>-8.52</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>9</v>
       </c>
@@ -14249,7 +14248,7 @@
         <v>-8.51</v>
       </c>
     </row>
-    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>9</v>
       </c>
@@ -14279,7 +14278,7 @@
         <v>-2.71</v>
       </c>
     </row>
-    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>9</v>
       </c>
@@ -14309,7 +14308,7 @@
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>9</v>
       </c>
@@ -14339,7 +14338,7 @@
         <v>-15.580000000000002</v>
       </c>
     </row>
-    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>9</v>
       </c>
@@ -14369,7 +14368,7 @@
         <v>110.44000000000003</v>
       </c>
     </row>
-    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>9</v>
       </c>
@@ -14399,7 +14398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>9</v>
       </c>
@@ -14429,7 +14428,7 @@
         <v>-2.84</v>
       </c>
     </row>
-    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>9</v>
       </c>
@@ -14459,7 +14458,7 @@
         <v>-62.769999999999982</v>
       </c>
     </row>
-    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>9</v>
       </c>
@@ -14489,7 +14488,7 @@
         <v>59.22</v>
       </c>
     </row>
-    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>9</v>
       </c>
@@ -14519,7 +14518,7 @@
         <v>-196.19</v>
       </c>
     </row>
-    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>9</v>
       </c>
@@ -14549,7 +14548,7 @@
         <v>92.560000000000016</v>
       </c>
     </row>
-    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>9</v>
       </c>
@@ -14579,7 +14578,7 @@
         <v>-1.34</v>
       </c>
     </row>
-    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>9</v>
       </c>
@@ -14609,7 +14608,7 @@
         <v>55.500000000000028</v>
       </c>
     </row>
-    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>9</v>
       </c>
@@ -14639,7 +14638,7 @@
         <v>-28.549999999999997</v>
       </c>
     </row>
-    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>9</v>
       </c>
@@ -14669,7 +14668,7 @@
         <v>102.66999999999997</v>
       </c>
     </row>
-    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>9</v>
       </c>
@@ -14699,7 +14698,7 @@
         <v>-141.48000000000005</v>
       </c>
     </row>
-    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>9</v>
       </c>
@@ -14729,7 +14728,7 @@
         <v>-1.54</v>
       </c>
     </row>
-    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>9</v>
       </c>
@@ -14759,7 +14758,7 @@
         <v>-82.589999999999989</v>
       </c>
     </row>
-    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>9</v>
       </c>
@@ -14789,7 +14788,7 @@
         <v>1251.8000000000002</v>
       </c>
     </row>
-    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>9</v>
       </c>
@@ -14819,7 +14818,7 @@
         <v>-33.20999999999998</v>
       </c>
     </row>
-    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>9</v>
       </c>
@@ -14849,7 +14848,7 @@
         <v>70.56</v>
       </c>
     </row>
-    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>9</v>
       </c>
@@ -14879,7 +14878,7 @@
         <v>23.580000000000002</v>
       </c>
     </row>
-    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>9</v>
       </c>
@@ -14909,7 +14908,7 @@
         <v>59.02000000000001</v>
       </c>
     </row>
-    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>9</v>
       </c>
@@ -14939,7 +14938,7 @@
         <v>-866.68000000000029</v>
       </c>
     </row>
-    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>9</v>
       </c>
@@ -14969,7 +14968,7 @@
         <v>-76.259999999999977</v>
       </c>
     </row>
-    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>9</v>
       </c>
@@ -14999,7 +14998,7 @@
         <v>-35.569999999999993</v>
       </c>
     </row>
-    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>9</v>
       </c>
@@ -15029,7 +15028,7 @@
         <v>17.299999999999997</v>
       </c>
     </row>
-    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>9</v>
       </c>
@@ -15059,7 +15058,7 @@
         <v>-1.83</v>
       </c>
     </row>
-    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>9</v>
       </c>
@@ -15089,7 +15088,7 @@
         <v>-52.660000000000004</v>
       </c>
     </row>
-    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>9</v>
       </c>
@@ -15119,7 +15118,7 @@
         <v>-5.66</v>
       </c>
     </row>
-    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>9</v>
       </c>
@@ -15149,7 +15148,7 @@
         <v>-18.53</v>
       </c>
     </row>
-    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>9</v>
       </c>
@@ -15179,7 +15178,7 @@
         <v>189.08</v>
       </c>
     </row>
-    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>9</v>
       </c>
@@ -15209,7 +15208,7 @@
         <v>-11.65</v>
       </c>
     </row>
-    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>9</v>
       </c>
@@ -15239,7 +15238,7 @@
         <v>118.69999999999999</v>
       </c>
     </row>
-    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>9</v>
       </c>
@@ -15269,7 +15268,7 @@
         <v>-1.1299999999999999</v>
       </c>
     </row>
-    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>9</v>
       </c>
@@ -15299,7 +15298,7 @@
         <v>-4.9800000000000004</v>
       </c>
     </row>
-    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>9</v>
       </c>
@@ -15329,7 +15328,7 @@
         <v>-147.36999999999995</v>
       </c>
     </row>
-    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>9</v>
       </c>
@@ -15359,7 +15358,7 @@
         <v>-1.64</v>
       </c>
     </row>
-    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>9</v>
       </c>
@@ -15389,7 +15388,7 @@
         <v>-36.230000000000032</v>
       </c>
     </row>
-    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>9</v>
       </c>
@@ -15419,7 +15418,7 @@
         <v>-15.270000000000001</v>
       </c>
     </row>
-    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>9</v>
       </c>
@@ -15449,7 +15448,7 @@
         <v>-20.020000000000003</v>
       </c>
     </row>
-    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>9</v>
       </c>
@@ -15479,7 +15478,7 @@
         <v>-56.56</v>
       </c>
     </row>
-    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>9</v>
       </c>
@@ -15509,7 +15508,7 @@
         <v>197.83</v>
       </c>
     </row>
-    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>9</v>
       </c>
@@ -15539,7 +15538,7 @@
         <v>62.35</v>
       </c>
     </row>
-    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>9</v>
       </c>
@@ -15569,7 +15568,7 @@
         <v>22.72</v>
       </c>
     </row>
-    <row r="492" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>9</v>
       </c>
@@ -15599,7 +15598,7 @@
         <v>43.569999999999993</v>
       </c>
     </row>
-    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>9</v>
       </c>
@@ -15629,7 +15628,7 @@
         <v>78.28</v>
       </c>
     </row>
-    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>9</v>
       </c>
@@ -15659,7 +15658,7 @@
         <v>-68.42</v>
       </c>
     </row>
-    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>9</v>
       </c>
@@ -15689,7 +15688,7 @@
         <v>31.280000000000008</v>
       </c>
     </row>
-    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>9</v>
       </c>
@@ -15719,7 +15718,7 @@
         <v>-2.0499999999999998</v>
       </c>
     </row>
-    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>9</v>
       </c>
@@ -15749,7 +15748,7 @@
         <v>116.16</v>
       </c>
     </row>
-    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>9</v>
       </c>
@@ -15779,7 +15778,7 @@
         <v>-5.9000000000000057</v>
       </c>
     </row>
-    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>9</v>
       </c>
@@ -15809,7 +15808,7 @@
         <v>-20.209999999999997</v>
       </c>
     </row>
-    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>9</v>
       </c>
@@ -15839,7 +15838,7 @@
         <v>-0.97</v>
       </c>
     </row>
-    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>9</v>
       </c>
@@ -15869,7 +15868,7 @@
         <v>72.089999999999989</v>
       </c>
     </row>
-    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>9</v>
       </c>
@@ -15899,7 +15898,7 @@
         <v>-66.240000000000038</v>
       </c>
     </row>
-    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>9</v>
       </c>
@@ -15929,7 +15928,7 @@
         <v>21.009999999999998</v>
       </c>
     </row>
-    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>9</v>
       </c>
@@ -15959,7 +15958,7 @@
         <v>18.43</v>
       </c>
     </row>
-    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>9</v>
       </c>
@@ -15989,7 +15988,7 @@
         <v>3.919999999999991</v>
       </c>
     </row>
-    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>9</v>
       </c>
@@ -16019,7 +16018,7 @@
         <v>10.29</v>
       </c>
     </row>
-    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>9</v>
       </c>
@@ -16049,7 +16048,7 @@
         <v>-1.6100000000000421</v>
       </c>
     </row>
-    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>9</v>
       </c>
@@ -16079,7 +16078,7 @@
         <v>-6.98</v>
       </c>
     </row>
-    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>9</v>
       </c>
@@ -16109,7 +16108,7 @@
         <v>-3.65</v>
       </c>
     </row>
-    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>9</v>
       </c>
@@ -16139,7 +16138,7 @@
         <v>18.579999999999998</v>
       </c>
     </row>
-    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>9</v>
       </c>
@@ -16169,7 +16168,7 @@
         <v>-6.8900000000000006</v>
       </c>
     </row>
-    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>9</v>
       </c>
@@ -16199,7 +16198,7 @@
         <v>-27.449999999999982</v>
       </c>
     </row>
-    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>9</v>
       </c>
@@ -16229,7 +16228,7 @@
         <v>95.73</v>
       </c>
     </row>
-    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>9</v>
       </c>
@@ -16259,7 +16258,7 @@
         <v>109.20000000000002</v>
       </c>
     </row>
-    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>9</v>
       </c>
@@ -16289,7 +16288,7 @@
         <v>87.93</v>
       </c>
     </row>
-    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>9</v>
       </c>
@@ -16319,7 +16318,7 @@
         <v>-2.6000000000000156</v>
       </c>
     </row>
-    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>9</v>
       </c>
@@ -16349,7 +16348,7 @@
         <v>28.990000000000002</v>
       </c>
     </row>
-    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>9</v>
       </c>
@@ -16379,7 +16378,7 @@
         <v>-6.6800000000000068</v>
       </c>
     </row>
-    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>9</v>
       </c>
@@ -16409,7 +16408,7 @@
         <v>-31.989999999999981</v>
       </c>
     </row>
-    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>9</v>
       </c>
@@ -16439,7 +16438,7 @@
         <v>-51.169999999999987</v>
       </c>
     </row>
-    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>9</v>
       </c>
@@ -16469,7 +16468,7 @@
         <v>-44.360000000000007</v>
       </c>
     </row>
-    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>9</v>
       </c>
@@ -16499,7 +16498,7 @@
         <v>-35.6</v>
       </c>
     </row>
-    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>9</v>
       </c>
@@ -16529,7 +16528,7 @@
         <v>-17.570000000000004</v>
       </c>
     </row>
-    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>9</v>
       </c>
@@ -16559,7 +16558,7 @@
         <v>-27.33</v>
       </c>
     </row>
-    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>9</v>
       </c>
@@ -16589,7 +16588,7 @@
         <v>-23.06</v>
       </c>
     </row>
-    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>9</v>
       </c>
@@ -16619,7 +16618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>9</v>
       </c>
@@ -16649,7 +16648,7 @@
         <v>132.69999999999999</v>
       </c>
     </row>
-    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>9</v>
       </c>
@@ -16679,7 +16678,7 @@
         <v>16.93</v>
       </c>
     </row>
-    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>9</v>
       </c>
@@ -16709,7 +16708,7 @@
         <v>113.58999999999999</v>
       </c>
     </row>
-    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>9</v>
       </c>
@@ -16739,7 +16738,7 @@
         <v>-3.9099999999999997</v>
       </c>
     </row>
-    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>9</v>
       </c>
@@ -16769,7 +16768,7 @@
         <v>-176.92000000000007</v>
       </c>
     </row>
-    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>9</v>
       </c>
@@ -16799,7 +16798,7 @@
         <v>-14.29</v>
       </c>
     </row>
-    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>9</v>
       </c>
@@ -16829,7 +16828,7 @@
         <v>7.2199999999999989</v>
       </c>
     </row>
-    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>9</v>
       </c>
@@ -16859,7 +16858,7 @@
         <v>-195.73000000000002</v>
       </c>
     </row>
-    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>9</v>
       </c>
@@ -16889,7 +16888,7 @@
         <v>-9.17</v>
       </c>
     </row>
-    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>9</v>
       </c>
@@ -16919,7 +16918,7 @@
         <v>-1.98</v>
       </c>
     </row>
-    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>9</v>
       </c>
@@ -16949,7 +16948,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>9</v>
       </c>
@@ -16979,7 +16978,7 @@
         <v>-1.02</v>
       </c>
     </row>
-    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>9</v>
       </c>
@@ -17009,7 +17008,7 @@
         <v>15.169999999999998</v>
       </c>
     </row>
-    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>9</v>
       </c>
@@ -17039,7 +17038,7 @@
         <v>13.93</v>
       </c>
     </row>
-    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>9</v>
       </c>
@@ -17069,7 +17068,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>9</v>
       </c>
@@ -17099,7 +17098,7 @@
         <v>11.869999999999997</v>
       </c>
     </row>
-    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>9</v>
       </c>
@@ -17129,7 +17128,7 @@
         <v>-0.49</v>
       </c>
     </row>
-    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>9</v>
       </c>
@@ -17159,7 +17158,7 @@
         <v>-1.37</v>
       </c>
     </row>
-    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>9</v>
       </c>
@@ -17189,7 +17188,7 @@
         <v>4.4499999999999993</v>
       </c>
     </row>
-    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>9</v>
       </c>
@@ -17219,7 +17218,7 @@
         <v>391.03999999999996</v>
       </c>
     </row>
-    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>9</v>
       </c>
@@ -17249,7 +17248,7 @@
         <v>16.13</v>
       </c>
     </row>
-    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>9</v>
       </c>
@@ -17279,7 +17278,7 @@
         <v>17.97</v>
       </c>
     </row>
-    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>9</v>
       </c>
@@ -17309,7 +17308,7 @@
         <v>48.39</v>
       </c>
     </row>
-    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>9</v>
       </c>
@@ -17339,7 +17338,7 @@
         <v>308.22000000000003</v>
       </c>
     </row>
-    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>9</v>
       </c>
@@ -17369,7 +17368,7 @@
         <v>-143.87</v>
       </c>
     </row>
-    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>9</v>
       </c>
@@ -17399,7 +17398,7 @@
         <v>-2.74</v>
       </c>
     </row>
-    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>9</v>
       </c>
@@ -17429,7 +17428,7 @@
         <v>-13.790000000000001</v>
       </c>
     </row>
-    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>9</v>
       </c>
@@ -17459,7 +17458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>40</v>
       </c>
@@ -17489,7 +17488,7 @@
         <v>-371.53999999999985</v>
       </c>
     </row>
-    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>40</v>
       </c>
@@ -17519,7 +17518,7 @@
         <v>-26.310000000000002</v>
       </c>
     </row>
-    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>40</v>
       </c>
@@ -17549,7 +17548,7 @@
         <v>-48.16</v>
       </c>
     </row>
-    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>40</v>
       </c>
@@ -17579,7 +17578,7 @@
         <v>-6.19</v>
       </c>
     </row>
-    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>37</v>
       </c>
@@ -17609,7 +17608,7 @@
         <v>-0.32</v>
       </c>
     </row>
-    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>37</v>
       </c>
@@ -17639,7 +17638,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>37</v>
       </c>
@@ -17669,7 +17668,7 @@
         <v>-0.79</v>
       </c>
     </row>
-    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>37</v>
       </c>
@@ -17699,7 +17698,7 @@
         <v>-7.2799999999999994</v>
       </c>
     </row>
-    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>37</v>
       </c>
@@ -17729,7 +17728,7 @@
         <v>220.77000000000007</v>
       </c>
     </row>
-    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>37</v>
       </c>
@@ -17759,7 +17758,7 @@
         <v>18.82</v>
       </c>
     </row>
-    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>37</v>
       </c>
@@ -17789,7 +17788,7 @@
         <v>20.009999999999998</v>
       </c>
     </row>
-    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>37</v>
       </c>
@@ -17819,7 +17818,7 @@
         <v>93.339999999999989</v>
       </c>
     </row>
-    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>37</v>
       </c>
@@ -17849,7 +17848,7 @@
         <v>19.02</v>
       </c>
     </row>
-    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>37</v>
       </c>
@@ -17879,7 +17878,7 @@
         <v>38.909999999999997</v>
       </c>
     </row>
-    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>37</v>
       </c>
@@ -17909,7 +17908,7 @@
         <v>-305.43999999999994</v>
       </c>
     </row>
-    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>37</v>
       </c>
@@ -17939,7 +17938,7 @@
         <v>24.68</v>
       </c>
     </row>
-    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>37</v>
       </c>
@@ -17969,7 +17968,7 @@
         <v>61.37</v>
       </c>
     </row>
-    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>37</v>
       </c>
@@ -17999,7 +17998,7 @@
         <v>315.29000000000008</v>
       </c>
     </row>
-    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>37</v>
       </c>
@@ -18029,7 +18028,7 @@
         <v>-9.9400000000000013</v>
       </c>
     </row>
-    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>37</v>
       </c>
@@ -18059,7 +18058,7 @@
         <v>-34.08</v>
       </c>
     </row>
-    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>37</v>
       </c>
@@ -18089,7 +18088,7 @@
         <v>-2.16</v>
       </c>
     </row>
-    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>37</v>
       </c>
@@ -18119,7 +18118,7 @@
         <v>-9.8099999999999987</v>
       </c>
     </row>
-    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>37</v>
       </c>
@@ -18149,7 +18148,7 @@
         <v>-59.390000000000015</v>
       </c>
     </row>
-    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>37</v>
       </c>
@@ -18179,7 +18178,7 @@
         <v>7.6000000000000014</v>
       </c>
     </row>
-    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>37</v>
       </c>
@@ -18209,7 +18208,7 @@
         <v>301.52999999999997</v>
       </c>
     </row>
-    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>37</v>
       </c>
@@ -18239,7 +18238,7 @@
         <v>-284.67999999999938</v>
       </c>
     </row>
-    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>37</v>
       </c>
@@ -18269,7 +18268,7 @@
         <v>-3.02</v>
       </c>
     </row>
-    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>37</v>
       </c>
@@ -18299,7 +18298,7 @@
         <v>-1.51</v>
       </c>
     </row>
-    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>37</v>
       </c>
@@ -18329,7 +18328,7 @@
         <v>64.58</v>
       </c>
     </row>
-    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>37</v>
       </c>
@@ -18359,7 +18358,7 @@
         <v>-0.94</v>
       </c>
     </row>
-    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>37</v>
       </c>
@@ -18389,7 +18388,7 @@
         <v>157.51</v>
       </c>
     </row>
-    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>37</v>
       </c>
@@ -18419,7 +18418,7 @@
         <v>-3.12</v>
       </c>
     </row>
-    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>37</v>
       </c>
@@ -18449,7 +18448,7 @@
         <v>-385.57000000000011</v>
       </c>
     </row>
-    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>37</v>
       </c>
@@ -18479,7 +18478,7 @@
         <v>-59.599999999999994</v>
       </c>
     </row>
-    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>37</v>
       </c>
@@ -18509,7 +18508,7 @@
         <v>200.71999999999997</v>
       </c>
     </row>
-    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>37</v>
       </c>
@@ -18539,7 +18538,7 @@
         <v>-1.7</v>
       </c>
     </row>
-    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>37</v>
       </c>
@@ -18569,7 +18568,7 @@
         <v>22.560000000000002</v>
       </c>
     </row>
-    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>37</v>
       </c>
@@ -18599,7 +18598,7 @@
         <v>59.36</v>
       </c>
     </row>
-    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>37</v>
       </c>
@@ -18629,7 +18628,7 @@
         <v>-144.3300000000001</v>
       </c>
     </row>
-    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>37</v>
       </c>
@@ -18659,7 +18658,7 @@
         <v>24.459999999999997</v>
       </c>
     </row>
-    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>37</v>
       </c>
@@ -18689,7 +18688,7 @@
         <v>-12.320000000000007</v>
       </c>
     </row>
-    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>37</v>
       </c>
@@ -18719,7 +18718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>37</v>
       </c>
@@ -18749,7 +18748,7 @@
         <v>-100.39999999999998</v>
       </c>
     </row>
-    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>37</v>
       </c>
@@ -18779,7 +18778,7 @@
         <v>42.709999999999994</v>
       </c>
     </row>
-    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>37</v>
       </c>
@@ -18809,7 +18808,7 @@
         <v>-62.349999999999994</v>
       </c>
     </row>
-    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>37</v>
       </c>
@@ -18839,7 +18838,7 @@
         <v>-36.4</v>
       </c>
     </row>
-    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>37</v>
       </c>
@@ -18869,7 +18868,7 @@
         <v>306.05000000000007</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>37</v>
       </c>
@@ -18899,7 +18898,7 @@
         <v>1.6299999999999955</v>
       </c>
     </row>
-    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>37</v>
       </c>
@@ -18929,7 +18928,7 @@
         <v>1.1899999999999995</v>
       </c>
     </row>
-    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>37</v>
       </c>
@@ -18959,7 +18958,7 @@
         <v>553.12</v>
       </c>
     </row>
-    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>37</v>
       </c>
@@ -18989,7 +18988,7 @@
         <v>29.239999999999995</v>
       </c>
     </row>
-    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>37</v>
       </c>
@@ -19019,7 +19018,7 @@
         <v>-16.59</v>
       </c>
     </row>
-    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>37</v>
       </c>
@@ -19049,7 +19048,7 @@
         <v>352.71</v>
       </c>
     </row>
-    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>37</v>
       </c>
@@ -19079,7 +19078,7 @@
         <v>142.22999999999999</v>
       </c>
     </row>
-    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>37</v>
       </c>
@@ -19109,7 +19108,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>37</v>
       </c>
@@ -19139,7 +19138,7 @@
         <v>-216.15999999999983</v>
       </c>
     </row>
-    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>37</v>
       </c>
@@ -19169,7 +19168,7 @@
         <v>110.66</v>
       </c>
     </row>
-    <row r="612" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>37</v>
       </c>
@@ -19199,7 +19198,7 @@
         <v>-78.319999999999993</v>
       </c>
     </row>
-    <row r="613" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>37</v>
       </c>
@@ -19229,7 +19228,7 @@
         <v>-4.180000000000291</v>
       </c>
     </row>
-    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>37</v>
       </c>
@@ -19259,7 +19258,7 @@
         <v>-16.920000000000009</v>
       </c>
     </row>
-    <row r="615" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>37</v>
       </c>
@@ -19289,7 +19288,7 @@
         <v>22.640000000000004</v>
       </c>
     </row>
-    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>37</v>
       </c>
@@ -19319,7 +19318,7 @@
         <v>-238.52999999999997</v>
       </c>
     </row>
-    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>37</v>
       </c>
@@ -19349,7 +19348,7 @@
         <v>48.910000000000025</v>
       </c>
     </row>
-    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>37</v>
       </c>
@@ -19379,7 +19378,7 @@
         <v>155.30000000000001</v>
       </c>
     </row>
-    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>37</v>
       </c>
@@ -19409,7 +19408,7 @@
         <v>-42.11999999999999</v>
       </c>
     </row>
-    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>37</v>
       </c>
@@ -19439,7 +19438,7 @@
         <v>101.25</v>
       </c>
     </row>
-    <row r="621" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>37</v>
       </c>
@@ -19469,7 +19468,7 @@
         <v>-1.92</v>
       </c>
     </row>
-    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>37</v>
       </c>
@@ -19499,7 +19498,7 @@
         <v>-290.78999999999996</v>
       </c>
     </row>
-    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>37</v>
       </c>
@@ -19529,7 +19528,7 @@
         <v>-27.410000000000007</v>
       </c>
     </row>
-    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>37</v>
       </c>
@@ -19559,7 +19558,7 @@
         <v>-34.72</v>
       </c>
     </row>
-    <row r="625" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>37</v>
       </c>
@@ -19589,7 +19588,7 @@
         <v>40.44</v>
       </c>
     </row>
-    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>37</v>
       </c>
@@ -19619,7 +19618,7 @@
         <v>-242.6399999999999</v>
       </c>
     </row>
-    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>37</v>
       </c>
@@ -19649,7 +19648,7 @@
         <v>301.75999999999988</v>
       </c>
     </row>
-    <row r="628" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>37</v>
       </c>
@@ -19679,7 +19678,7 @@
         <v>130.61000000000001</v>
       </c>
     </row>
-    <row r="629" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>37</v>
       </c>
@@ -19709,7 +19708,7 @@
         <v>-260.02999999999992</v>
       </c>
     </row>
-    <row r="630" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>37</v>
       </c>
@@ -19739,7 +19738,7 @@
         <v>-22.15</v>
       </c>
     </row>
-    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>37</v>
       </c>
@@ -19769,7 +19768,7 @@
         <v>-297.10000000000019</v>
       </c>
     </row>
-    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>11</v>
       </c>
@@ -19799,7 +19798,7 @@
         <v>-15.98</v>
       </c>
     </row>
-    <row r="633" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>11</v>
       </c>
@@ -19829,7 +19828,7 @@
         <v>-29.200000000000003</v>
       </c>
     </row>
-    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>11</v>
       </c>
@@ -19859,7 +19858,7 @@
         <v>34.11</v>
       </c>
     </row>
-    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>11</v>
       </c>
@@ -19889,7 +19888,7 @@
         <v>-92.760000000000019</v>
       </c>
     </row>
-    <row r="636" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>11</v>
       </c>
@@ -19919,7 +19918,7 @@
         <v>-168.45000000000005</v>
       </c>
     </row>
-    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>11</v>
       </c>
@@ -19949,7 +19948,7 @@
         <v>-130.98000000000002</v>
       </c>
     </row>
-    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>11</v>
       </c>
@@ -19979,7 +19978,7 @@
         <v>18.13</v>
       </c>
     </row>
-    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>11</v>
       </c>
@@ -20009,7 +20008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>11</v>
       </c>
@@ -20039,7 +20038,7 @@
         <v>36.18</v>
       </c>
     </row>
-    <row r="641" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>11</v>
       </c>
@@ -20069,7 +20068,7 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="642" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>11</v>
       </c>
@@ -20099,7 +20098,7 @@
         <v>20.81</v>
       </c>
     </row>
-    <row r="643" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>11</v>
       </c>
@@ -20129,7 +20128,7 @@
         <v>-4.84</v>
       </c>
     </row>
-    <row r="644" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>11</v>
       </c>
@@ -20159,7 +20158,7 @@
         <v>-43.04</v>
       </c>
     </row>
-    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>11</v>
       </c>
@@ -20189,7 +20188,7 @@
         <v>-1.87</v>
       </c>
     </row>
-    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>11</v>
       </c>
@@ -20219,7 +20218,7 @@
         <v>-11.32</v>
       </c>
     </row>
-    <row r="647" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>11</v>
       </c>
@@ -20249,7 +20248,7 @@
         <v>-13.139999999999999</v>
       </c>
     </row>
-    <row r="648" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>11</v>
       </c>
@@ -20279,7 +20278,7 @@
         <v>-24.52</v>
       </c>
     </row>
-    <row r="649" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>11</v>
       </c>
@@ -20309,7 +20308,7 @@
         <v>-13.720000000000002</v>
       </c>
     </row>
-    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>11</v>
       </c>
@@ -20339,7 +20338,7 @@
         <v>-39.630000000000003</v>
       </c>
     </row>
-    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>11</v>
       </c>
@@ -20369,7 +20368,7 @@
         <v>-0.93</v>
       </c>
     </row>
-    <row r="652" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>11</v>
       </c>
@@ -20399,7 +20398,7 @@
         <v>-12.03</v>
       </c>
     </row>
-    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>11</v>
       </c>
@@ -20429,7 +20428,7 @@
         <v>-2.4500000000000002</v>
       </c>
     </row>
-    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>11</v>
       </c>
@@ -20459,7 +20458,7 @@
         <v>-1.6400000000000001</v>
       </c>
     </row>
-    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>11</v>
       </c>
@@ -20489,7 +20488,7 @@
         <v>-1.92</v>
       </c>
     </row>
-    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>11</v>
       </c>
@@ -20519,7 +20518,7 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>11</v>
       </c>
@@ -20549,7 +20548,7 @@
         <v>-6.1199999999999992</v>
       </c>
     </row>
-    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>11</v>
       </c>
@@ -20579,7 +20578,7 @@
         <v>-0.96</v>
       </c>
     </row>
-    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>13</v>
       </c>
@@ -20609,7 +20608,7 @@
         <v>54.11999999999999</v>
       </c>
     </row>
-    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>13</v>
       </c>
@@ -20639,7 +20638,7 @@
         <v>-4.09</v>
       </c>
     </row>
-    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>13</v>
       </c>
@@ -20669,7 +20668,7 @@
         <v>12.440000000000001</v>
       </c>
     </row>
-    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>13</v>
       </c>
@@ -20699,7 +20698,7 @@
         <v>-1.88</v>
       </c>
     </row>
-    <row r="663" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>13</v>
       </c>
@@ -20729,7 +20728,7 @@
         <v>-68.379999999999981</v>
       </c>
     </row>
-    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>13</v>
       </c>
@@ -20759,7 +20758,7 @@
         <v>-0.45</v>
       </c>
     </row>
-    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>13</v>
       </c>
@@ -20789,7 +20788,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>13</v>
       </c>
@@ -20819,7 +20818,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>13</v>
       </c>
@@ -20849,7 +20848,7 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>13</v>
       </c>
@@ -20879,7 +20878,7 @@
         <v>-8.01</v>
       </c>
     </row>
-    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>13</v>
       </c>
@@ -20909,7 +20908,7 @@
         <v>-4.57</v>
       </c>
     </row>
-    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>13</v>
       </c>
@@ -20939,7 +20938,7 @@
         <v>-7.669999999999999</v>
       </c>
     </row>
-    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>13</v>
       </c>
@@ -20969,7 +20968,7 @@
         <v>-1.64</v>
       </c>
     </row>
-    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>13</v>
       </c>
@@ -20999,7 +20998,7 @@
         <v>-7.1999999999999993</v>
       </c>
     </row>
-    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>13</v>
       </c>
@@ -21029,7 +21028,7 @@
         <v>12.819999999999999</v>
       </c>
     </row>
-    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>13</v>
       </c>
@@ -21059,7 +21058,7 @@
         <v>0.15999999999999998</v>
       </c>
     </row>
-    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>13</v>
       </c>
@@ -21089,7 +21088,7 @@
         <v>-0.22</v>
       </c>
     </row>
-    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>13</v>
       </c>
@@ -21119,7 +21118,7 @@
         <v>-0.68</v>
       </c>
     </row>
-    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>13</v>
       </c>
@@ -21149,7 +21148,7 @@
         <v>-0.90000000000000013</v>
       </c>
     </row>
-    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>13</v>
       </c>
@@ -21179,7 +21178,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>13</v>
       </c>
@@ -21209,7 +21208,7 @@
         <v>20.309999999999999</v>
       </c>
     </row>
-    <row r="680" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>13</v>
       </c>
@@ -21239,7 +21238,7 @@
         <v>-1.52</v>
       </c>
     </row>
-    <row r="681" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>13</v>
       </c>
@@ -21269,7 +21268,7 @@
         <v>-0.23</v>
       </c>
     </row>
-    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>13</v>
       </c>
@@ -21299,7 +21298,7 @@
         <v>-3.6</v>
       </c>
     </row>
-    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>13</v>
       </c>
@@ -21329,7 +21328,7 @@
         <v>-7.1099999999999994</v>
       </c>
     </row>
-    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>13</v>
       </c>
@@ -21359,7 +21358,7 @@
         <v>33.46</v>
       </c>
     </row>
-    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>13</v>
       </c>
@@ -21389,7 +21388,7 @@
         <v>-0.34</v>
       </c>
     </row>
-    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>13</v>
       </c>
@@ -21419,7 +21418,7 @@
         <v>-1.23</v>
       </c>
     </row>
-    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>13</v>
       </c>
@@ -21449,7 +21448,7 @@
         <v>-0.34</v>
       </c>
     </row>
-    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>13</v>
       </c>
@@ -21479,7 +21478,7 @@
         <v>27.48</v>
       </c>
     </row>
-    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>13</v>
       </c>
@@ -21509,7 +21508,7 @@
         <v>128.63000000000002</v>
       </c>
     </row>
-    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>13</v>
       </c>
@@ -21539,7 +21538,7 @@
         <v>15.32</v>
       </c>
     </row>
-    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>13</v>
       </c>
@@ -21569,7 +21568,7 @@
         <v>19.350000000000001</v>
       </c>
     </row>
-    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>13</v>
       </c>
@@ -21599,7 +21598,7 @@
         <v>196.28999999999996</v>
       </c>
     </row>
-    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>13</v>
       </c>
@@ -21629,7 +21628,7 @@
         <v>26.470000000000002</v>
       </c>
     </row>
-    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>13</v>
       </c>
@@ -21659,7 +21658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>13</v>
       </c>
@@ -21689,7 +21688,7 @@
         <v>-5.64</v>
       </c>
     </row>
-    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>13</v>
       </c>
@@ -21719,7 +21718,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>13</v>
       </c>
@@ -21749,7 +21748,7 @@
         <v>287.96000000000004</v>
       </c>
     </row>
-    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>13</v>
       </c>
@@ -21779,7 +21778,7 @@
         <v>186.57</v>
       </c>
     </row>
-    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>13</v>
       </c>
@@ -21809,7 +21808,7 @@
         <v>-10.879999999999999</v>
       </c>
     </row>
-    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>13</v>
       </c>
@@ -21839,7 +21838,7 @@
         <v>128.31</v>
       </c>
     </row>
-    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>13</v>
       </c>
@@ -21869,7 +21868,7 @@
         <v>-141.53999999999996</v>
       </c>
     </row>
-    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>13</v>
       </c>
@@ -21899,7 +21898,7 @@
         <v>121.09999999999994</v>
       </c>
     </row>
-    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>13</v>
       </c>
@@ -21929,7 +21928,7 @@
         <v>-4.5299999999999994</v>
       </c>
     </row>
-    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>13</v>
       </c>
@@ -21959,7 +21958,7 @@
         <v>-124.32</v>
       </c>
     </row>
-    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>13</v>
       </c>
@@ -21989,7 +21988,7 @@
         <v>-23.33</v>
       </c>
     </row>
-    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>13</v>
       </c>
@@ -22019,7 +22018,7 @@
         <v>-49.209999999999987</v>
       </c>
     </row>
-    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>13</v>
       </c>
@@ -22049,7 +22048,7 @@
         <v>-0.32</v>
       </c>
     </row>
-    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>13</v>
       </c>
@@ -22079,7 +22078,7 @@
         <v>-42.28</v>
       </c>
     </row>
-    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>13</v>
       </c>
@@ -22109,7 +22108,7 @@
         <v>-282.52999999999975</v>
       </c>
     </row>
-    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>13</v>
       </c>
@@ -22139,7 +22138,7 @@
         <v>-232.44999999999973</v>
       </c>
     </row>
-    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>13</v>
       </c>
@@ -22169,7 +22168,7 @@
         <v>-9.1399999999999988</v>
       </c>
     </row>
-    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>13</v>
       </c>
@@ -22199,7 +22198,7 @@
         <v>-163.81999999999991</v>
       </c>
     </row>
-    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>13</v>
       </c>
@@ -22229,7 +22228,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>13</v>
       </c>
@@ -22259,7 +22258,7 @@
         <v>-133.44999999999973</v>
       </c>
     </row>
-    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>13</v>
       </c>
@@ -22289,7 +22288,7 @@
         <v>45.74</v>
       </c>
     </row>
-    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>13</v>
       </c>
@@ -22319,7 +22318,7 @@
         <v>-10.41</v>
       </c>
     </row>
-    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>13</v>
       </c>
@@ -22349,7 +22348,7 @@
         <v>14.469999999999999</v>
       </c>
     </row>
-    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>13</v>
       </c>
@@ -22379,7 +22378,7 @@
         <v>63.15</v>
       </c>
     </row>
-    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>13</v>
       </c>
@@ -22409,7 +22408,7 @@
         <v>18.43</v>
       </c>
     </row>
-    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>13</v>
       </c>
@@ -22439,7 +22438,7 @@
         <v>19.350000000000001</v>
       </c>
     </row>
-    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>13</v>
       </c>
@@ -22469,7 +22468,7 @@
         <v>209.46</v>
       </c>
     </row>
-    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>13</v>
       </c>
@@ -22499,7 +22498,7 @@
         <v>-10.95</v>
       </c>
     </row>
-    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>13</v>
       </c>
@@ -22529,7 +22528,7 @@
         <v>-5.8999999999999995</v>
       </c>
     </row>
-    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>13</v>
       </c>
@@ -22559,7 +22558,7 @@
         <v>-27.320000000000007</v>
       </c>
     </row>
-    <row r="725" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>13</v>
       </c>
@@ -22589,7 +22588,7 @@
         <v>-27.260000000000005</v>
       </c>
     </row>
-    <row r="726" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>13</v>
       </c>
@@ -22619,7 +22618,7 @@
         <v>-9.6</v>
       </c>
     </row>
-    <row r="727" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>13</v>
       </c>
@@ -22649,7 +22648,7 @@
         <v>-94.149999999999977</v>
       </c>
     </row>
-    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>13</v>
       </c>
@@ -22679,7 +22678,7 @@
         <v>-1.64</v>
       </c>
     </row>
-    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>13</v>
       </c>
@@ -22709,7 +22708,7 @@
         <v>-8.2899999999999991</v>
       </c>
     </row>
-    <row r="730" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>13</v>
       </c>
@@ -22739,7 +22738,7 @@
         <v>-2.74</v>
       </c>
     </row>
-    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>13</v>
       </c>
@@ -22769,7 +22768,7 @@
         <v>-16.3</v>
       </c>
     </row>
-    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>13</v>
       </c>
@@ -22799,7 +22798,7 @@
         <v>38.35</v>
       </c>
     </row>
-    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>13</v>
       </c>
@@ -22829,7 +22828,7 @@
         <v>-266.30999999999955</v>
       </c>
     </row>
-    <row r="734" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>13</v>
       </c>
@@ -22859,7 +22858,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>13</v>
       </c>
@@ -22889,7 +22888,7 @@
         <v>-15.8</v>
       </c>
     </row>
-    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>13</v>
       </c>
@@ -22919,7 +22918,7 @@
         <v>-2.98</v>
       </c>
     </row>
-    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>13</v>
       </c>
@@ -22949,7 +22948,7 @@
         <v>8.9400000000000013</v>
       </c>
     </row>
-    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>13</v>
       </c>
@@ -22979,7 +22978,7 @@
         <v>-8.2799999999999994</v>
       </c>
     </row>
-    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>13</v>
       </c>
@@ -23009,7 +23008,7 @@
         <v>46.02</v>
       </c>
     </row>
-    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>13</v>
       </c>
@@ -23039,7 +23038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>13</v>
       </c>
@@ -23069,7 +23068,7 @@
         <v>-2.74</v>
       </c>
     </row>
-    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>13</v>
       </c>
@@ -23099,7 +23098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="743" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>13</v>
       </c>
@@ -23129,7 +23128,7 @@
         <v>240.96999999999997</v>
       </c>
     </row>
-    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>13</v>
       </c>
@@ -23159,7 +23158,7 @@
         <v>-35.900000000000006</v>
       </c>
     </row>
-    <row r="745" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>13</v>
       </c>
@@ -23189,7 +23188,7 @@
         <v>66.930000000000007</v>
       </c>
     </row>
-    <row r="746" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>13</v>
       </c>
@@ -23219,7 +23218,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="747" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>13</v>
       </c>
@@ -23249,7 +23248,7 @@
         <v>-7.8199999999999994</v>
       </c>
     </row>
-    <row r="748" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>13</v>
       </c>
@@ -23279,7 +23278,7 @@
         <v>61.110000000000007</v>
       </c>
     </row>
-    <row r="749" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>13</v>
       </c>
@@ -23309,7 +23308,7 @@
         <v>-30.57</v>
       </c>
     </row>
-    <row r="750" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>13</v>
       </c>
@@ -23339,7 +23338,7 @@
         <v>-3.28</v>
       </c>
     </row>
-    <row r="751" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>13</v>
       </c>
@@ -23369,7 +23368,7 @@
         <v>-72.269999999999982</v>
       </c>
     </row>
-    <row r="752" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>13</v>
       </c>
@@ -23399,7 +23398,7 @@
         <v>-13.95</v>
       </c>
     </row>
-    <row r="753" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>13</v>
       </c>
@@ -23429,7 +23428,7 @@
         <v>-0.22</v>
       </c>
     </row>
-    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>13</v>
       </c>
@@ -23459,7 +23458,7 @@
         <v>-38.110000000000014</v>
       </c>
     </row>
-    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>21</v>
       </c>
@@ -23489,7 +23488,7 @@
         <v>-173.93999999999994</v>
       </c>
     </row>
-    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>21</v>
       </c>
@@ -23519,7 +23518,7 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="757" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>21</v>
       </c>
@@ -23549,7 +23548,7 @@
         <v>-64.239999999999981</v>
       </c>
     </row>
-    <row r="758" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>21</v>
       </c>
@@ -23579,7 +23578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>21</v>
       </c>
@@ -23609,7 +23608,7 @@
         <v>-13.590000000000002</v>
       </c>
     </row>
-    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>21</v>
       </c>
@@ -23639,7 +23638,7 @@
         <v>-36.070000000000007</v>
       </c>
     </row>
-    <row r="761" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>21</v>
       </c>
@@ -23669,7 +23668,7 @@
         <v>-45.489999999999995</v>
       </c>
     </row>
-    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>21</v>
       </c>
@@ -23699,7 +23698,7 @@
         <v>-1.71</v>
       </c>
     </row>
-    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>21</v>
       </c>
@@ -23729,7 +23728,7 @@
         <v>-4.38</v>
       </c>
     </row>
-    <row r="764" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>21</v>
       </c>
@@ -23759,7 +23758,7 @@
         <v>17.48</v>
       </c>
     </row>
-    <row r="765" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>21</v>
       </c>
@@ -23789,7 +23788,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>21</v>
       </c>
@@ -23819,7 +23818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="767" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>21</v>
       </c>
@@ -23849,7 +23848,7 @@
         <v>-0.98</v>
       </c>
     </row>
-    <row r="768" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>21</v>
       </c>
@@ -23879,7 +23878,7 @@
         <v>-20.34</v>
       </c>
     </row>
-    <row r="769" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>21</v>
       </c>
@@ -23909,7 +23908,7 @@
         <v>-2.29</v>
       </c>
     </row>
-    <row r="770" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>21</v>
       </c>
@@ -23939,7 +23938,7 @@
         <v>-4.9400000000000004</v>
       </c>
     </row>
-    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>21</v>
       </c>
@@ -23969,7 +23968,7 @@
         <v>-5.82</v>
       </c>
     </row>
-    <row r="772" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>21</v>
       </c>
@@ -23999,7 +23998,7 @@
         <v>-2.5799999999999996</v>
       </c>
     </row>
-    <row r="773" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>21</v>
       </c>
@@ -24029,7 +24028,7 @@
         <v>-4.21</v>
       </c>
     </row>
-    <row r="774" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>21</v>
       </c>
@@ -24059,7 +24058,7 @@
         <v>60.739999999999995</v>
       </c>
     </row>
-    <row r="775" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>21</v>
       </c>
@@ -24089,7 +24088,7 @@
         <v>-10.280000000000001</v>
       </c>
     </row>
-    <row r="776" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>21</v>
       </c>
@@ -24119,7 +24118,7 @@
         <v>-13.960000000000003</v>
       </c>
     </row>
-    <row r="777" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>21</v>
       </c>
@@ -24149,7 +24148,7 @@
         <v>-1.96</v>
       </c>
     </row>
-    <row r="778" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>21</v>
       </c>
@@ -24179,7 +24178,7 @@
         <v>-12.97</v>
       </c>
     </row>
-    <row r="779" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>21</v>
       </c>
@@ -24209,7 +24208,7 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="780" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>21</v>
       </c>
@@ -24239,7 +24238,7 @@
         <v>-2.8899999999999997</v>
       </c>
     </row>
-    <row r="781" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>21</v>
       </c>
@@ -24269,7 +24268,7 @@
         <v>-11.24</v>
       </c>
     </row>
-    <row r="782" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>21</v>
       </c>
@@ -24299,7 +24298,7 @@
         <v>3.2399999999999998</v>
       </c>
     </row>
-    <row r="783" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>21</v>
       </c>
@@ -24329,7 +24328,7 @@
         <v>-1.1399999999999999</v>
       </c>
     </row>
-    <row r="784" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>21</v>
       </c>
@@ -24359,7 +24358,7 @@
         <v>-13.41</v>
       </c>
     </row>
-    <row r="785" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>21</v>
       </c>
@@ -24389,7 +24388,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="786" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>21</v>
       </c>
@@ -24419,7 +24418,7 @@
         <v>42.589999999999996</v>
       </c>
     </row>
-    <row r="787" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>21</v>
       </c>
@@ -24449,7 +24448,7 @@
         <v>-0.56000000000000005</v>
       </c>
     </row>
-    <row r="788" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>21</v>
       </c>
@@ -24479,7 +24478,7 @@
         <v>39.660000000000004</v>
       </c>
     </row>
-    <row r="789" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>21</v>
       </c>
@@ -24509,7 +24508,7 @@
         <v>27.779999999999998</v>
       </c>
     </row>
-    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>21</v>
       </c>
@@ -24539,7 +24538,7 @@
         <v>12.93</v>
       </c>
     </row>
-    <row r="791" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>21</v>
       </c>
@@ -24569,7 +24568,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="792" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>21</v>
       </c>
@@ -24599,7 +24598,7 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>21</v>
       </c>
@@ -24629,7 +24628,7 @@
         <v>20.71</v>
       </c>
     </row>
-    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>21</v>
       </c>
@@ -24659,7 +24658,7 @@
         <v>-1.4300000000000002</v>
       </c>
     </row>
-    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>21</v>
       </c>
@@ -24689,7 +24688,7 @@
         <v>-0.09</v>
       </c>
     </row>
-    <row r="796" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>21</v>
       </c>
@@ -24719,7 +24718,7 @@
         <v>-1.17</v>
       </c>
     </row>
-    <row r="797" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>21</v>
       </c>
@@ -24749,7 +24748,7 @@
         <v>-41.769999999999989</v>
       </c>
     </row>
-    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>21</v>
       </c>
@@ -24779,7 +24778,7 @@
         <v>49.580000000000005</v>
       </c>
     </row>
-    <row r="799" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>21</v>
       </c>
@@ -24809,7 +24808,7 @@
         <v>-49.410000000000004</v>
       </c>
     </row>
-    <row r="800" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>21</v>
       </c>
@@ -24839,7 +24838,7 @@
         <v>-8.4499999999999975</v>
       </c>
     </row>
-    <row r="801" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>21</v>
       </c>
@@ -24869,7 +24868,7 @@
         <v>-11.39</v>
       </c>
     </row>
-    <row r="802" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>21</v>
       </c>
@@ -24899,7 +24898,7 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="803" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>21</v>
       </c>
@@ -24929,7 +24928,7 @@
         <v>-7.9</v>
       </c>
     </row>
-    <row r="804" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>21</v>
       </c>
@@ -24959,7 +24958,7 @@
         <v>-8.4600000000000009</v>
       </c>
     </row>
-    <row r="805" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>21</v>
       </c>
@@ -24989,7 +24988,7 @@
         <v>2.8199999999999967</v>
       </c>
     </row>
-    <row r="806" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>21</v>
       </c>
@@ -25019,7 +25018,7 @@
         <v>-3.9000000000000004</v>
       </c>
     </row>
-    <row r="807" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>21</v>
       </c>
@@ -25049,7 +25048,7 @@
         <v>-1.81</v>
       </c>
     </row>
-    <row r="808" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>21</v>
       </c>
@@ -25079,7 +25078,7 @@
         <v>-13.129999999999997</v>
       </c>
     </row>
-    <row r="809" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>21</v>
       </c>
@@ -25109,7 +25108,7 @@
         <v>-43.569999999999986</v>
       </c>
     </row>
-    <row r="810" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>21</v>
       </c>
@@ -25139,7 +25138,7 @@
         <v>-2.2399999999999998</v>
       </c>
     </row>
-    <row r="811" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>21</v>
       </c>
@@ -25169,7 +25168,7 @@
         <v>-1.02</v>
       </c>
     </row>
-    <row r="812" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>21</v>
       </c>
@@ -25199,7 +25198,7 @@
         <v>-7.61</v>
       </c>
     </row>
-    <row r="813" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>21</v>
       </c>
@@ -25229,7 +25228,7 @@
         <v>-3.1500000000000004</v>
       </c>
     </row>
-    <row r="814" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>21</v>
       </c>
@@ -25259,7 +25258,7 @@
         <v>8.2899999999999991</v>
       </c>
     </row>
-    <row r="815" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>21</v>
       </c>
@@ -25289,7 +25288,7 @@
         <v>-5.8</v>
       </c>
     </row>
-    <row r="816" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>21</v>
       </c>
@@ -25319,7 +25318,7 @@
         <v>-1.3</v>
       </c>
     </row>
-    <row r="817" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>21</v>
       </c>
@@ -25349,7 +25348,7 @@
         <v>-2.75</v>
       </c>
     </row>
-    <row r="818" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>21</v>
       </c>
@@ -25379,7 +25378,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="819" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>21</v>
       </c>
@@ -25409,7 +25408,7 @@
         <v>23.15</v>
       </c>
     </row>
-    <row r="820" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>21</v>
       </c>
@@ -25439,7 +25438,7 @@
         <v>-0.84000000000000008</v>
       </c>
     </row>
-    <row r="821" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>21</v>
       </c>
@@ -25469,7 +25468,7 @@
         <v>-0.32</v>
       </c>
     </row>
-    <row r="822" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>21</v>
       </c>
@@ -25499,7 +25498,7 @@
         <v>19.88</v>
       </c>
     </row>
-    <row r="823" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>21</v>
       </c>
@@ -25529,7 +25528,7 @@
         <v>5.0500000000000007</v>
       </c>
     </row>
-    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>21</v>
       </c>
@@ -25559,7 +25558,7 @@
         <v>-1.05</v>
       </c>
     </row>
-    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>21</v>
       </c>
@@ -25589,7 +25588,7 @@
         <v>-0.97</v>
       </c>
     </row>
-    <row r="826" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>21</v>
       </c>
@@ -25619,7 +25618,7 @@
         <v>-31.289999999999996</v>
       </c>
     </row>
-    <row r="827" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>23</v>
       </c>
@@ -25649,7 +25648,7 @@
         <v>-10.819999999999999</v>
       </c>
     </row>
-    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>23</v>
       </c>
@@ -25679,7 +25678,7 @@
         <v>-2.99</v>
       </c>
     </row>
-    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>23</v>
       </c>
@@ -25709,7 +25708,7 @@
         <v>-23.769999999999996</v>
       </c>
     </row>
-    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>23</v>
       </c>
@@ -25739,7 +25738,7 @@
         <v>-4.68</v>
       </c>
     </row>
-    <row r="831" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>23</v>
       </c>
@@ -25769,7 +25768,7 @@
         <v>-0.62</v>
       </c>
     </row>
-    <row r="832" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>23</v>
       </c>
@@ -25799,7 +25798,7 @@
         <v>-9.51</v>
       </c>
     </row>
-    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>23</v>
       </c>
@@ -25829,7 +25828,7 @@
         <v>-0.33</v>
       </c>
     </row>
-    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>23</v>
       </c>
@@ -25859,7 +25858,7 @@
         <v>-1.52</v>
       </c>
     </row>
-    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>23</v>
       </c>
@@ -25889,7 +25888,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="836" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>23</v>
       </c>
@@ -25919,7 +25918,7 @@
         <v>573.62</v>
       </c>
     </row>
-    <row r="837" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>23</v>
       </c>
@@ -25949,7 +25948,7 @@
         <v>63.749999999999993</v>
       </c>
     </row>
-    <row r="838" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>5</v>
       </c>
@@ -25979,7 +25978,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="839" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>5</v>
       </c>
@@ -26009,7 +26008,7 @@
         <v>19.21</v>
       </c>
     </row>
-    <row r="840" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>23</v>
       </c>
@@ -26039,7 +26038,7 @@
         <v>11.43</v>
       </c>
     </row>
-    <row r="841" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>21</v>
       </c>
@@ -26069,7 +26068,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="842" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>52</v>
       </c>
@@ -26099,7 +26098,7 @@
         <v>17.62</v>
       </c>
     </row>
-    <row r="843" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>52</v>
       </c>
@@ -26129,7 +26128,7 @@
         <v>-6.19</v>
       </c>
     </row>
-    <row r="844" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>5</v>
       </c>
@@ -26159,7 +26158,7 @@
         <v>-553.46000000000015</v>
       </c>
     </row>
-    <row r="845" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>5</v>
       </c>
@@ -26189,7 +26188,7 @@
         <v>-0.96</v>
       </c>
     </row>
-    <row r="846" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>37</v>
       </c>
@@ -26219,28 +26218,28 @@
         <v>-31.289999999999996</v>
       </c>
     </row>
-    <row r="847" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E847" s="2"/>
       <c r="F847" s="2"/>
       <c r="G847" s="2"/>
       <c r="H847" s="2"/>
       <c r="I847" s="2"/>
     </row>
-    <row r="848" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E848" s="2"/>
       <c r="F848" s="2"/>
       <c r="G848" s="2"/>
       <c r="H848" s="2"/>
       <c r="I848" s="2"/>
     </row>
-    <row r="849" spans="5:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E849" s="2"/>
       <c r="F849" s="2"/>
       <c r="G849" s="2"/>
       <c r="H849" s="2"/>
       <c r="I849" s="2"/>
     </row>
-    <row r="850" spans="5:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="5:9" x14ac:dyDescent="0.25">
       <c r="E850" s="2"/>
       <c r="F850" s="2"/>
       <c r="G850" s="2"/>
@@ -26253,18 +26252,7 @@
       <c r="I851" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I850" xr:uid="{C919F51F-D068-4207-A728-1B1A2EAAFF8C}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Middle East"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="OECD Europe"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I850" xr:uid="{C919F51F-D068-4207-A728-1B1A2EAAFF8C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <customProperties>
     <customPr name="GUID" r:id="rId1"/>
@@ -26277,7 +26265,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71D1E016-DD03-42BD-8141-BE001A011503}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FACC00E-2E12-46E1-886D-FB50DB7E3332}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="urn:argus-direct-storage:queries"/>
   </ds:schemaRefs>
